--- a/data/Rickenbach (LU)/cost/cost_report.xlsx
+++ b/data/Rickenbach (LU)/cost/cost_report.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>624.9947400498198</v>
+        <v>475.35362162672</v>
       </c>
       <c r="C2" t="n">
-        <v>29762.32934323403</v>
+        <v>35211.58738994353</v>
       </c>
       <c r="D2" t="n">
-        <v>-47045.63470313613</v>
+        <v>-59196.20694194647</v>
       </c>
       <c r="E2" t="n">
-        <v>7124.224970270356</v>
+        <v>6495.96561197963</v>
       </c>
       <c r="F2" t="n">
-        <v>48126.61237903823</v>
+        <v>54219.66949269834</v>
       </c>
       <c r="G2" t="n">
-        <v>38592.52672945631</v>
+        <v>37206.36917430175</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.07609484539172311</v>
+        <v>1.760680515014778</v>
       </c>
     </row>
     <row r="3">
@@ -515,22 +515,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>626.3396283234168</v>
+        <v>472.3527894445864</v>
       </c>
       <c r="C3" t="n">
-        <v>27747.67300693358</v>
+        <v>34972.77099820855</v>
       </c>
       <c r="D3" t="n">
-        <v>-40179.46346855054</v>
+        <v>-58659.88872132819</v>
       </c>
       <c r="E3" t="n">
-        <v>4646.868290170996</v>
+        <v>6481.175788188244</v>
       </c>
       <c r="F3" t="n">
-        <v>46509.77233923845</v>
+        <v>54970.77740217819</v>
       </c>
       <c r="G3" t="n">
-        <v>39351.18979611591</v>
+        <v>38237.18825669138</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.07759073989913844</v>
+        <v>1.809460955384176</v>
       </c>
     </row>
     <row r="4">
@@ -548,30 +548,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>633.8156038295397</v>
+        <v>495.9263687122868</v>
       </c>
       <c r="C4" t="n">
-        <v>9134.230541151928</v>
+        <v>9188.142765895445</v>
       </c>
       <c r="D4" t="n">
-        <v>33361.61084619241</v>
+        <v>37086.90191134519</v>
       </c>
       <c r="E4" t="n">
-        <v>2683.941240759107</v>
+        <v>2029.685482317961</v>
       </c>
       <c r="F4" t="n">
-        <v>18348.08131624651</v>
+        <v>15804.30161305473</v>
       </c>
       <c r="G4" t="n">
-        <v>64161.67954817949</v>
+        <v>64604.95814132561</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cp_cu</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.126510842876879</v>
+        <v>3.057237067124062</v>
       </c>
     </row>
     <row r="5">
@@ -581,30 +581,30 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>633.7495170154228</v>
+        <v>497.7989117605143</v>
       </c>
       <c r="C5" t="n">
-        <v>9071.641977119494</v>
+        <v>9166.377256320691</v>
       </c>
       <c r="D5" t="n">
-        <v>33865.61568717989</v>
+        <v>36581.78047258982</v>
       </c>
       <c r="E5" t="n">
-        <v>2680.910556803946</v>
+        <v>2020.208381308939</v>
       </c>
       <c r="F5" t="n">
-        <v>17379.38426683661</v>
+        <v>16905.29352047103</v>
       </c>
       <c r="G5" t="n">
-        <v>63631.30200495536</v>
+        <v>65171.45854245099</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>cp_cu</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.1254650705325645</v>
+        <v>3.084045009961398</v>
       </c>
     </row>
   </sheetData>
